--- a/Piaui/2026/Julho/ResultadosTRI_3EM_LP/Simulado_III/ResumoThetaIC_3EM_LP_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_LP/Simulado_III/ResumoThetaIC_3EM_LP_S3.xlsx
@@ -395,22 +395,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>235.388</v>
+        <v>235.383</v>
       </c>
       <c r="C2" t="n">
-        <v>234.24</v>
+        <v>234.235</v>
       </c>
       <c r="D2" t="n">
-        <v>236.536</v>
+        <v>236.53</v>
       </c>
       <c r="E2" t="n">
-        <v>82.203</v>
+        <v>82.161</v>
       </c>
       <c r="F2" t="n">
-        <v>80.036</v>
+        <v>79.995</v>
       </c>
       <c r="G2" t="n">
-        <v>84.371</v>
+        <v>84.328</v>
       </c>
     </row>
     <row r="3">
@@ -427,13 +427,13 @@
         <v>-0.269</v>
       </c>
       <c r="E3" t="n">
-        <v>1.644</v>
+        <v>1.643</v>
       </c>
       <c r="F3" t="n">
-        <v>1.62</v>
+        <v>1.619</v>
       </c>
       <c r="G3" t="n">
-        <v>1.668</v>
+        <v>1.667</v>
       </c>
     </row>
   </sheetData>
